--- a/04_DESIGN_TABLES/DesignTable_2408_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2408_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD16"/>
+  <dimension ref="A1:AD17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1670,29 +1670,29 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2408-16-SOLID</t>
+          <t>2408-14-SOLID</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="C12" t="n">
-        <v>0.79674</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="E12" t="n">
-        <v>0.65625</v>
+        <v>0.59375</v>
       </c>
       <c r="F12" t="n">
         <v>0.125</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4365</v>
+        <v>0.4155</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5965</v>
+        <v>0.534</v>
       </c>
       <c r="I12" t="n">
         <v>0.1292</v>
@@ -1707,13 +1707,13 @@
         <v>37</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3125</v>
+        <v>1.1875</v>
       </c>
       <c r="N12" t="n">
         <v>0.08333</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7305</v>
       </c>
       <c r="P12" t="n">
         <v>0.04511</v>
@@ -1731,12 +1731,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2408-16-SOLID</t>
+          <t>2408-14-SOLID</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Male Plug (37 deg JIC), 1 5/16-12 (solid)</t>
+          <t>Male Plug (37 deg JIC), 1 3/16-12 (solid)</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1751,62 +1751,62 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>1 3/16-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan fleet; L/hex: Air-Way==MS51518 | MODEL: JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L3/hex: Air-Way == MS51518D; plug head = hex to a plain flat face (Brennan 2408-08 STEP: hex 0.283 long = L3 - JIC end length, 75deg chamfers not modelled); HOLLOW (-H) configs: blind hole HOLE from the JIC tip to depth = JIC end length - 0.020 (ASSUMPTION - measured on the Brennan 2408-08 STEP only: 0.391 hole, full diameter to 0.637 = 0.657 - 0.020, 120deg drill point not modelled); SOLID configs: hole feature suppressed</t>
+          <t>[BRENNAN-CELL 2026-10-20: HEXB@HEX] JIC end: MS33656J==Brennan fleet; L3 1.31: Air-Way == Brennan TFA p66 "L LGTH" 1.310; THDMAJ_B@DRIVE 1.1875 = JIC -14 thread major (gen_straight2 JIC[14] = 2403 table, = the row's own EndB_Thread 1 3/16-12): repairs the 2026-09 column shift (the cell held the voted hex 1.25); HEXB@HEX: Brennan TFA catalog p.66 table TFA-p066-t05 "MJ PLUG" row 2408-14 col "C HEX" = 1.250 (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_index.json, page verified True) [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan ("use brennans")] (Air-Way printed 1.125: the hex (1.125 across the flats) is smaller than its own 1 3/16-12 JIC thread (major 1.1875); MS51518D prints 1 1/4 (this row's 2026-09 $COMMENT)) | MODEL: JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L3/hex: Air-Way == MS51518D; plug head = hex to a plain flat face (Brennan 2408-08 STEP: hex 0.283 long = L3 - JIC end length, 75deg chamfers not modelled); HOLLOW (-H) configs: blind hole HOLE from the JIC tip to depth = JIC end length - 0.020 (ASSUMPTION - measured on the Brennan 2408-08 STEP only: 0.391 hole, full diameter to 0.637 = 0.657 - 0.020, 120deg drill point not modelled); SOLID configs: hole feature suppressed</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>MS51518D L/hex AGREE | BUILD (OMi SKU does not state solid/hollow - matched to every plug variant of this size)</t>
+          <t>CONFLICT vs MS51518 hex: AW 1.125 vs MS 1 1/4 | BUILD (OMi SKU does not state solid/hollow - matched to every plug variant of this size) | 2026-10-20 HEXB@HEX = Brennan 1.25 (Air-Way 1.125 cannot be built: the hex (1.125 across the flats) is smaller than its own 1 3/16-12 JIC thread (major 1.1875); MS51518D prints 1 1/4 (this row's 2026-09 $COMMENT))</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2408-16</t>
+          <t>2408-14</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2408-20-H</t>
+          <t>2408-16-SOLID</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="C13" t="n">
-        <v>0.97572</v>
+        <v>0.79674</v>
       </c>
       <c r="D13" t="n">
-        <v>1.69</v>
+        <v>1.38</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="F13" t="n">
         <v>0.125</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="H13" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="K13" t="n">
         <v>60</v>
@@ -1815,13 +1815,13 @@
         <v>37</v>
       </c>
       <c r="M13" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="N13" t="n">
         <v>0.08333</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7986</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="P13" t="n">
         <v>0.04511</v>
@@ -1832,25 +1832,19 @@
       <c r="R13" t="n">
         <v>0.08333</v>
       </c>
-      <c r="S13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.9379999999999999</v>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>S</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2408-20-H</t>
+          <t>2408-16-SOLID</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Male Plug (37 deg JIC), 1 5/8-12 (hollow)</t>
+          <t>Male Plug (37 deg JIC), 1 5/16-12 (solid)</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -1865,12 +1859,12 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -1880,19 +1874,19 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>MS51518D L/hex AGREE | BUILD (OMi SKU does not state solid/hollow - matched to every plug variant of this size) | HOLE DEPTH single-source (JIC end length - 0.020, measured on the Brennan 2408-08 STEP only) -&gt; DataStatus ASSUMED</t>
+          <t>MS51518D L/hex AGREE | BUILD (OMi SKU does not state solid/hollow - matched to every plug variant of this size)</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2408-20</t>
+          <t>2408-16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2408-20-SOLID</t>
+          <t>2408-20-H</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1946,19 +1940,25 @@
       <c r="R14" t="n">
         <v>0.08333</v>
       </c>
+      <c r="S14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.9379999999999999</v>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>U</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2408-20-SOLID</t>
+          <t>2408-20-H</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Male Plug (37 deg JIC), 1 5/8-12 (solid)</t>
+          <t>Male Plug (37 deg JIC), 1 5/8-12 (hollow)</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>MS51518D L/hex AGREE | BUILD (OMi SKU does not state solid/hollow - matched to every plug variant of this size)</t>
+          <t>MS51518D L/hex AGREE | BUILD (OMi SKU does not state solid/hollow - matched to every plug variant of this size) | HOLE DEPTH single-source (JIC end length - 0.020, measured on the Brennan 2408-08 STEP only) -&gt; DataStatus ASSUMED</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2000,35 +2000,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2408-24-H</t>
+          <t>2408-20-SOLID</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="C15" t="n">
-        <v>1.1547</v>
+        <v>0.97572</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="F15" t="n">
         <v>0.125</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1298</v>
+        <v>0.1288</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="K15" t="n">
         <v>60</v>
@@ -2037,13 +2037,13 @@
         <v>37</v>
       </c>
       <c r="M15" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="N15" t="n">
         <v>0.08333</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9234</v>
+        <v>0.7986</v>
       </c>
       <c r="P15" t="n">
         <v>0.04511</v>
@@ -2054,25 +2054,19 @@
       <c r="R15" t="n">
         <v>0.08333</v>
       </c>
-      <c r="S15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.063</v>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>S</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2408-24-H</t>
+          <t>2408-20-SOLID</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Male Plug (37 deg JIC), 1 7/8-12 (hollow)</t>
+          <t>Male Plug (37 deg JIC), 1 5/8-12 (solid)</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2087,12 +2081,12 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1 7/8-12</t>
+          <t>1 5/8-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2102,47 +2096,47 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>MS51518D L/hex AGREE | BUILD (OMi SKU does not state solid/hollow - matched to every plug variant of this size) | HOLE DEPTH single-source (JIC end length - 0.020, measured on the Brennan 2408-08 STEP only) -&gt; DataStatus ASSUMED</t>
+          <t>MS51518D L/hex AGREE | BUILD (OMi SKU does not state solid/hollow - matched to every plug variant of this size)</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2408-24</t>
+          <t>2408-20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2408-32-H</t>
+          <t>2408-24-H</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="C16" t="n">
-        <v>1.51843</v>
+        <v>1.1547</v>
       </c>
       <c r="D16" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="F16" t="n">
         <v>0.125</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7124</v>
+        <v>0.5454</v>
       </c>
       <c r="H16" t="n">
-        <v>1.19</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1292</v>
+        <v>0.1298</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3318</v>
+        <v>0.2482</v>
       </c>
       <c r="K16" t="n">
         <v>60</v>
@@ -2151,13 +2145,13 @@
         <v>37</v>
       </c>
       <c r="M16" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="N16" t="n">
         <v>0.08333</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1734</v>
+        <v>0.9234</v>
       </c>
       <c r="P16" t="n">
         <v>0.04511</v>
@@ -2169,57 +2163,171 @@
         <v>0.08333</v>
       </c>
       <c r="S16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2408-24-H</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Male Plug (37 deg JIC), 1 7/8-12 (hollow)</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>plug head</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>1 7/8-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>JIC end: MS33656J==Brennan fleet; L/hex: Air-Way==MS51518 | MODEL: JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L3/hex: Air-Way == MS51518D; plug head = hex to a plain flat face (Brennan 2408-08 STEP: hex 0.283 long = L3 - JIC end length, 75deg chamfers not modelled); HOLLOW (-H) configs: blind hole HOLE from the JIC tip to depth = JIC end length - 0.020 (ASSUMPTION - measured on the Brennan 2408-08 STEP only: 0.391 hole, full diameter to 0.637 = 0.657 - 0.020, 120deg drill point not modelled); SOLID configs: hole feature suppressed</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>MS51518D L/hex AGREE | BUILD (OMi SKU does not state solid/hollow - matched to every plug variant of this size) | HOLE DEPTH single-source (JIC end length - 0.020, measured on the Brennan 2408-08 STEP only) -&gt; DataStatus ASSUMED</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>2408-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2408-32-H</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.51843</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="K17" t="n">
+        <v>60</v>
+      </c>
+      <c r="L17" t="n">
+        <v>37</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.1734</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S17" t="n">
         <v>1.78</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>1.313</v>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>2408-32-H</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Male Plug (37 deg JIC), 2 1/2-12 (hollow)</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>2408</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>plug head</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>2 1/2-12</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>JIC end: MS33656J==Brennan fleet; L/hex: Air-Way==MS51518 | MODEL: JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L3/hex: Air-Way == MS51518D; plug head = hex to a plain flat face (Brennan 2408-08 STEP: hex 0.283 long = L3 - JIC end length, 75deg chamfers not modelled); HOLLOW (-H) configs: blind hole HOLE from the JIC tip to depth = JIC end length - 0.020 (ASSUMPTION - measured on the Brennan 2408-08 STEP only: 0.391 hole, full diameter to 0.637 = 0.657 - 0.020, 120deg drill point not modelled); SOLID configs: hole feature suppressed</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>MS51518D L/hex AGREE | BUILD (OMi SKU does not state solid/hollow - matched to every plug variant of this size) | HOLE DEPTH single-source (JIC end length - 0.020, measured on the Brennan 2408-08 STEP only) -&gt; DataStatus ASSUMED</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>2408-32</t>
         </is>
